--- a/data/Privacy and protection of personal data (2020 onwards)_transformed.xlsx
+++ b/data/Privacy and protection of personal data (2020 onwards)_transformed.xlsx
@@ -453,12 +453,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -471,12 +471,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -491,12 +491,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -511,12 +511,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -531,12 +531,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -551,12 +551,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -571,12 +571,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -591,12 +591,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -611,12 +611,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -651,12 +651,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -671,12 +671,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -711,12 +711,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -731,12 +731,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -751,12 +751,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -771,12 +771,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -791,12 +791,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Összes személy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -829,12 +829,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -849,12 +849,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -869,12 +869,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -889,12 +889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -909,12 +909,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -929,12 +929,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -949,12 +949,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -969,12 +969,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -989,12 +989,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1029,12 +1029,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1049,12 +1049,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1069,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1089,12 +1089,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1109,12 +1109,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1129,12 +1129,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1149,12 +1149,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkavállalók, önálló vállalkozók, családi munkavállalók</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1169,12 +1169,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1187,12 +1187,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1207,12 +1207,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1247,12 +1247,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1267,12 +1267,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1287,12 +1287,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1347,12 +1347,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1367,12 +1367,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1407,12 +1407,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1427,12 +1427,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1467,12 +1467,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1487,12 +1487,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1507,12 +1507,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Nő, 16-74 éves</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1527,12 +1527,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1605,12 +1605,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1625,12 +1625,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1645,12 +1645,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1665,12 +1665,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1685,12 +1685,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1705,12 +1705,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1725,12 +1725,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1745,12 +1745,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1785,12 +1785,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1805,12 +1805,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1825,12 +1825,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1845,12 +1845,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1865,12 +1865,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermekes háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1885,12 +1885,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1943,12 +1943,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1983,12 +1983,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2003,12 +2003,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2023,12 +2023,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2043,12 +2043,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2083,12 +2083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2103,12 +2103,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2143,12 +2143,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2163,12 +2163,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2203,12 +2203,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2223,12 +2223,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Gyermek nélküli háztartásban élő személyek</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2243,12 +2243,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2281,12 +2281,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2321,12 +2321,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2361,12 +2361,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2401,12 +2401,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2421,12 +2421,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2441,12 +2441,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2481,12 +2481,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2501,12 +2501,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2521,12 +2521,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2541,12 +2541,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2581,12 +2581,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban élő személyek</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2619,12 +2619,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2659,12 +2659,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2699,12 +2699,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2719,12 +2719,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2739,12 +2739,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2759,12 +2759,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2779,12 +2779,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2819,12 +2819,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2839,12 +2839,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2859,12 +2859,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2879,12 +2879,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2899,12 +2899,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2919,12 +2919,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2939,12 +2939,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Vidéki területeken élő személyek</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2977,12 +2977,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3017,12 +3017,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3037,12 +3037,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3057,12 +3057,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3077,12 +3077,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3097,12 +3097,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3117,12 +3117,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3137,12 +3137,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3157,12 +3157,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3177,12 +3177,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3197,12 +3197,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3237,12 +3237,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3257,12 +3257,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3277,12 +3277,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3297,12 +3297,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Városokban és külvárosokban élő személyek</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3317,12 +3317,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3335,12 +3335,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3355,12 +3355,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3375,12 +3375,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3395,12 +3395,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3435,12 +3435,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3455,12 +3455,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3475,12 +3475,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3495,12 +3495,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3515,12 +3515,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3535,12 +3535,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3555,12 +3555,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3575,12 +3575,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3615,12 +3615,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3655,12 +3655,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Felsőfokú formális végzettséggel rendelkezők</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3675,12 +3675,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3693,12 +3693,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3713,12 +3713,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3733,12 +3733,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3753,12 +3753,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3773,12 +3773,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3793,12 +3793,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3813,12 +3813,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3833,12 +3833,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3853,12 +3853,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3873,12 +3873,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3893,12 +3893,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3913,12 +3913,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3933,12 +3933,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3953,12 +3953,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3973,12 +3973,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4013,12 +4013,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Közepes formális iskolai végzettséggel rendelkező személyek</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4033,12 +4033,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4051,12 +4051,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4071,12 +4071,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4091,12 +4091,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4111,12 +4111,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4131,12 +4131,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4151,12 +4151,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4171,12 +4171,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4191,12 +4191,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4211,12 +4211,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4231,12 +4231,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4251,12 +4251,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4271,12 +4271,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4291,12 +4291,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4311,12 +4311,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4331,12 +4331,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4351,12 +4351,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4371,12 +4371,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Formális végzettség nélküli vagy alacsony iskolázottságú személyek</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4391,12 +4391,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4409,12 +4409,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4427,12 +4427,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4445,12 +4445,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4463,12 +4463,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4481,12 +4481,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4499,12 +4499,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4535,12 +4535,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4553,12 +4553,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4571,12 +4571,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4589,12 +4589,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4607,12 +4607,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4625,12 +4625,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4643,12 +4643,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4661,12 +4661,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4679,12 +4679,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4697,12 +4697,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Egyének, 15 évesek vagy annál fiatalabbak</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4715,12 +4715,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4733,12 +4733,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4753,12 +4753,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4773,12 +4773,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4813,12 +4813,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4833,12 +4833,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4853,12 +4853,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4873,12 +4873,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4893,12 +4893,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4913,12 +4913,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4933,12 +4933,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -4953,12 +4953,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -4973,12 +4973,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -4993,12 +4993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5013,12 +5013,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5033,12 +5033,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5053,12 +5053,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>16-24 éves személyek</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5073,12 +5073,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5091,12 +5091,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5111,12 +5111,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5131,12 +5131,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5151,12 +5151,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5171,12 +5171,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5191,12 +5191,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5211,12 +5211,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5251,12 +5251,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5271,12 +5271,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5291,12 +5291,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5311,12 +5311,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5331,12 +5331,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5351,12 +5351,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5371,12 +5371,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5391,12 +5391,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5411,12 +5411,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>25-34 éves személyek</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5431,12 +5431,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -5449,12 +5449,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -5469,12 +5469,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -5509,12 +5509,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -5529,12 +5529,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -5549,12 +5549,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5569,12 +5569,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -5589,12 +5589,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -5609,12 +5609,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -5629,12 +5629,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -5649,12 +5649,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -5689,12 +5689,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -5709,12 +5709,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5729,12 +5729,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -5749,12 +5749,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5769,12 +5769,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>35-44 éves személyek</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5789,12 +5789,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5807,12 +5807,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5827,12 +5827,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5847,12 +5847,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -5867,12 +5867,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -5887,12 +5887,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -5907,12 +5907,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -5927,12 +5927,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -5947,12 +5947,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -5967,12 +5967,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -5987,12 +5987,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6007,12 +6007,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6027,12 +6027,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6047,12 +6047,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6067,12 +6067,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6087,12 +6087,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6127,12 +6127,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>45-54 éves személyek</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6147,12 +6147,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6165,12 +6165,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6185,12 +6185,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6205,12 +6205,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6225,12 +6225,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6245,12 +6245,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6265,12 +6265,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6285,12 +6285,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6305,12 +6305,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6325,12 +6325,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6345,12 +6345,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -6365,12 +6365,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -6385,12 +6385,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -6405,12 +6405,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -6425,12 +6425,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -6445,12 +6445,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -6465,12 +6465,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -6485,12 +6485,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>55-64 éves személyek</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -6505,12 +6505,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -6523,12 +6523,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -6543,12 +6543,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -6563,12 +6563,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -6583,12 +6583,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -6603,12 +6603,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -6623,12 +6623,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -6643,12 +6643,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -6663,12 +6663,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -6683,12 +6683,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -6703,12 +6703,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -6723,12 +6723,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -6743,12 +6743,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -6763,12 +6763,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -6783,12 +6783,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -6803,12 +6803,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -6823,12 +6823,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -6843,12 +6843,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>65-74 éves személyek</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -6863,12 +6863,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -6881,12 +6881,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -6899,12 +6899,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -6917,12 +6917,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -6935,12 +6935,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -6953,12 +6953,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -6971,12 +6971,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -6989,12 +6989,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7007,12 +7007,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7025,12 +7025,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7043,12 +7043,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7061,12 +7061,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7079,12 +7079,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7097,12 +7097,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7115,12 +7115,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7133,12 +7133,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7151,12 +7151,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7169,12 +7169,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>75 éves vagy idősebb személyek</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7187,12 +7187,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7205,12 +7205,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -7225,12 +7225,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -7245,12 +7245,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -7265,12 +7265,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -7285,12 +7285,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -7305,12 +7305,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -7325,12 +7325,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -7345,12 +7345,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -7365,12 +7365,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -7385,12 +7385,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -7405,12 +7405,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -7425,12 +7425,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -7445,12 +7445,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -7465,12 +7465,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -7485,12 +7485,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -7505,12 +7505,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -7525,12 +7525,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Férfiak, 16-74 évesek</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -7545,12 +7545,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -7563,12 +7563,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -7583,12 +7583,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -7603,12 +7603,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -7623,12 +7623,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -7643,12 +7643,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -7663,12 +7663,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -7683,12 +7683,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -7703,12 +7703,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -7723,12 +7723,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -7743,12 +7743,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -7763,12 +7763,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -7783,12 +7783,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -7803,12 +7803,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -7823,12 +7823,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -7843,12 +7843,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -7863,12 +7863,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -7883,12 +7883,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>hallgatók</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -7903,12 +7903,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -7921,12 +7921,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -7941,12 +7941,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): felkérték a webhelyeket vagy a keresőprogramok adminisztrátorát vagy szolgáltatóját, hogy hozzáférjenek a rólam tárolt adatokhoz, hogy frissítsék vagy töröljék azokat</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -7961,12 +7961,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -7981,12 +7981,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8001,12 +8001,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Magánszemélyek kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): ellenőrizte, hogy a weboldal, ahol a megadott személyes adatok biztonságosak voltak</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8021,12 +8021,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8041,12 +8041,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8061,12 +8061,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének kezelik a személyes adatokhoz való hozzáférést az interneten (3 hónap): korlátozott hozzáférés a profilhoz vagy a tartalomhoz a közösségi hálózatokon vagy a megosztott online tárhelyen</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -8081,12 +8081,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8101,12 +8101,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8121,12 +8121,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének az interneten keresztül kezelhetik a személyes adatokhoz való hozzáférést (3 hónap): a személyes adatok megadása előtt olvassa el az adatvédelmi nyilatkozatokat</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -8141,12 +8141,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -8161,12 +8161,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -8181,12 +8181,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): megtagadják a személyes adatok hirdetési célú felhasználásának engedélyezését</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -8201,12 +8201,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -8221,12 +8221,12 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -8241,12 +8241,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Munkanélküli</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  16 HOURS 17 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az egyének a személyes adatokhoz való hozzáférést az interneten kezelik (3 hónap): korlátozott vagy megtagadott hozzáférés a földrajzi helyhez</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
